--- a/demo/leveling_electrical.xlsx
+++ b/demo/leveling_electrical.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Generator &amp; ATS</t>
+          <t>Generator and ATS</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr"/>
@@ -890,16 +890,12 @@
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+      <c r="E22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Emergency lighting and exit signs</t>
+          <t>Fire stopping</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -914,7 +910,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Demolition of existing electrical systems</t>
+          <t>Emergency lighting and exit signs</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -933,65 +929,61 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Temporary power for construction</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr"/>
-      <c r="C25" s="13" t="inlineStr">
+          <t>Exterior lighting</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
+      <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+      <c r="E25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Trenching and backfill for site/exterior lighting conduits</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr"/>
+          <t>Conduit/raceway for excluded systems (fire alarm, low voltage)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Firestopping</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr"/>
+          <t>Grounding electrode system</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Testing and commissioning</t>
+          <t>Temporary power for construction</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr"/>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
+      <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr">
         <is>
           <t>⚠</t>
@@ -1001,32 +993,62 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Grounding and bonding systems</t>
+          <t>Demolition of existing electrical systems</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr"/>
       <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
+      <c r="E29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Patching and repair of finishes</t>
+          <t>Trenching and backfill for site lighting</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr"/>
       <c r="C30" s="7" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Firestopping</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Patching and painting</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1233,21 +1255,21 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>(p1) 1. Fire alarm system and devices EXCLUDED (by others).</t>
+          <t>(p1) Fire alarm system and devices EXCLUDED (by others).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>(p1) 2. Low voltage / data cabling not included.</t>
+          <t>(p1) Low voltage / data cabling not included.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>(p1) 3. Excludes temporary power and temporary lighting.</t>
+          <t>(p1) Excludes temporary power and temporary lighting.</t>
         </is>
       </c>
     </row>
